--- a/Hoadon/HD2026/HDVao/8/3502469834_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HD2026/HDVao/8/3502469834_HDDienTuDaCapMa.xlsx
@@ -397,6 +397,89 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C26TNT</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Số 412/32 Lê Hồng Phong, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>4770000.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>4770000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
